--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
@@ -525,6 +525,12 @@
       <c r="H2">
         <v>11.1</v>
       </c>
+      <c r="I2">
+        <v>33.3</v>
+      </c>
+      <c r="L2">
+        <v>13.7</v>
+      </c>
       <c r="R2" s="2">
         <v>26573</v>
       </c>
@@ -546,17 +552,23 @@
         <v>2</v>
       </c>
       <c r="D3">
-        <v>32.9</v>
+        <v>32.6</v>
       </c>
       <c r="E3">
         <v>10.8</v>
       </c>
       <c r="F3">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="H3">
         <v>12.2</v>
       </c>
+      <c r="I3">
+        <v>31.7</v>
+      </c>
+      <c r="L3">
+        <v>14</v>
+      </c>
       <c r="R3" s="2">
         <v>26574</v>
       </c>
@@ -578,17 +590,23 @@
         <v>3</v>
       </c>
       <c r="D4">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="E4">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="F4">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="H4">
         <v>12.2</v>
       </c>
+      <c r="I4">
+        <v>32.7</v>
+      </c>
+      <c r="L4">
+        <v>15.2</v>
+      </c>
       <c r="R4" s="2">
         <v>26575</v>
       </c>
@@ -610,10 +628,10 @@
         <v>4</v>
       </c>
       <c r="D5">
-        <v>35.2</v>
+        <v>35.3</v>
       </c>
       <c r="E5">
-        <v>10.9</v>
+        <v>11</v>
       </c>
       <c r="F5">
         <v>23.1</v>
@@ -621,6 +639,12 @@
       <c r="H5">
         <v>12.5</v>
       </c>
+      <c r="I5">
+        <v>34.7</v>
+      </c>
+      <c r="L5">
+        <v>13.8</v>
+      </c>
       <c r="R5" s="2">
         <v>26576</v>
       </c>
@@ -645,17 +669,20 @@
         <v>34.4</v>
       </c>
       <c r="E6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F6">
-        <v>27.7</v>
+        <v>22.7</v>
       </c>
       <c r="H6">
-        <v>19.9</v>
+        <v>19.1</v>
       </c>
       <c r="I6">
         <v>32.6</v>
       </c>
+      <c r="L6">
+        <v>15.1</v>
+      </c>
       <c r="R6" s="2">
         <v>26577</v>
       </c>
@@ -676,17 +703,17 @@
       <c r="C7">
         <v>6</v>
       </c>
-      <c r="D7">
-        <v>30.6</v>
-      </c>
-      <c r="E7">
-        <v>17.2</v>
-      </c>
-      <c r="F7">
-        <v>23.9</v>
-      </c>
-      <c r="K7">
-        <v>6.4</v>
+      <c r="G7">
+        <v>11.7</v>
+      </c>
+      <c r="H7">
+        <v>18.2</v>
+      </c>
+      <c r="I7">
+        <v>28.9</v>
+      </c>
+      <c r="J7">
+        <v>21.7</v>
       </c>
       <c r="R7" s="2">
         <v>26578</v>
@@ -708,8 +735,17 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="K8">
-        <v>12.7</v>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>18.5</v>
+      </c>
+      <c r="I8">
+        <v>31.3</v>
+      </c>
+      <c r="J8">
+        <v>27</v>
       </c>
       <c r="R8" s="2">
         <v>26579</v>
@@ -740,11 +776,20 @@
       <c r="F9">
         <v>24.9</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>16.6</v>
+      </c>
       <c r="I9">
         <v>33.2</v>
       </c>
-      <c r="K9">
-        <v>10.6</v>
+      <c r="J9">
+        <v>27</v>
+      </c>
+      <c r="M9">
+        <v>7.3</v>
       </c>
       <c r="R9" s="2">
         <v>26580</v>
@@ -767,16 +812,25 @@
         <v>9</v>
       </c>
       <c r="D10">
-        <v>31.4</v>
+        <v>31.8</v>
       </c>
       <c r="E10">
         <v>17.4</v>
       </c>
       <c r="F10">
-        <v>24.8</v>
-      </c>
-      <c r="K10">
-        <v>12</v>
+        <v>24.5</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>20.1</v>
+      </c>
+      <c r="I10">
+        <v>30.3</v>
+      </c>
+      <c r="J10">
+        <v>27</v>
       </c>
       <c r="R10" s="2">
         <v>26581</v>
@@ -798,8 +852,26 @@
       <c r="C11">
         <v>10</v>
       </c>
-      <c r="K11">
-        <v>10.4</v>
+      <c r="D11">
+        <v>31.2</v>
+      </c>
+      <c r="E11">
+        <v>15</v>
+      </c>
+      <c r="F11">
+        <v>23.2</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>16.5</v>
+      </c>
+      <c r="I11">
+        <v>31</v>
+      </c>
+      <c r="J11">
+        <v>27.1</v>
       </c>
       <c r="R11" s="2">
         <v>26582</v>
@@ -821,11 +893,14 @@
       <c r="C12">
         <v>11</v>
       </c>
-      <c r="K12">
-        <v>7.6</v>
-      </c>
-      <c r="L12">
-        <v>15.2</v>
+      <c r="D12">
+        <v>33</v>
+      </c>
+      <c r="E12">
+        <v>12.4</v>
+      </c>
+      <c r="F12">
+        <v>22.7</v>
       </c>
       <c r="R12" s="2">
         <v>26583</v>
@@ -859,9 +934,6 @@
       <c r="I13">
         <v>32</v>
       </c>
-      <c r="K13">
-        <v>7.9</v>
-      </c>
       <c r="L13">
         <v>0</v>
       </c>
@@ -885,11 +957,20 @@
       <c r="C14">
         <v>13</v>
       </c>
-      <c r="K14">
-        <v>12.6</v>
+      <c r="D14">
+        <v>23.4</v>
+      </c>
+      <c r="E14">
+        <v>17.2</v>
+      </c>
+      <c r="F14">
+        <v>20.3</v>
+      </c>
+      <c r="I14">
+        <v>28.3</v>
       </c>
       <c r="L14">
-        <v>14.6</v>
+        <v>5</v>
       </c>
       <c r="R14" s="2">
         <v>26585</v>
@@ -911,20 +992,14 @@
       <c r="C15">
         <v>14</v>
       </c>
-      <c r="I15">
-        <v>30.7</v>
-      </c>
-      <c r="J15">
-        <v>26.3</v>
-      </c>
-      <c r="K15">
-        <v>11.5</v>
-      </c>
-      <c r="L15">
-        <v>3</v>
-      </c>
-      <c r="M15">
-        <v>6.4</v>
+      <c r="D15">
+        <v>30.9</v>
+      </c>
+      <c r="E15">
+        <v>16.5</v>
+      </c>
+      <c r="F15">
+        <v>23.6</v>
       </c>
       <c r="R15" s="2">
         <v>26586</v>
@@ -947,19 +1022,13 @@
         <v>15</v>
       </c>
       <c r="D16">
-        <v>31.8</v>
+        <v>29.8</v>
       </c>
       <c r="E16">
         <v>15.2</v>
       </c>
       <c r="F16">
-        <v>23.5</v>
-      </c>
-      <c r="K16">
-        <v>10.7</v>
-      </c>
-      <c r="L16">
-        <v>14.5</v>
+        <v>22.5</v>
       </c>
       <c r="R16" s="2">
         <v>26587</v>
@@ -982,16 +1051,22 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>31.9</v>
+        <v>31.8</v>
       </c>
       <c r="E17">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="F17">
         <v>24.8</v>
       </c>
-      <c r="L17">
-        <v>14.8</v>
+      <c r="H17">
+        <v>19.8</v>
+      </c>
+      <c r="J17">
+        <v>17.7</v>
+      </c>
+      <c r="K17">
+        <v>11.8</v>
       </c>
       <c r="R17" s="2">
         <v>26588</v>
@@ -1022,8 +1097,14 @@
       <c r="F18">
         <v>22.6</v>
       </c>
-      <c r="L18">
-        <v>14.2</v>
+      <c r="H18">
+        <v>15.9</v>
+      </c>
+      <c r="J18">
+        <v>26.4</v>
+      </c>
+      <c r="K18">
+        <v>10.5</v>
       </c>
       <c r="R18" s="2">
         <v>26589</v>
@@ -1054,8 +1135,14 @@
       <c r="F19">
         <v>23.5</v>
       </c>
-      <c r="L19">
-        <v>14.5</v>
+      <c r="H19">
+        <v>16.3</v>
+      </c>
+      <c r="J19">
+        <v>27.2</v>
+      </c>
+      <c r="K19">
+        <v>10.8</v>
       </c>
       <c r="R19" s="2">
         <v>26590</v>
@@ -1086,8 +1173,14 @@
       <c r="F20">
         <v>23.9</v>
       </c>
-      <c r="L20">
-        <v>13.4</v>
+      <c r="H20">
+        <v>16.5</v>
+      </c>
+      <c r="J20">
+        <v>27.7</v>
+      </c>
+      <c r="K20">
+        <v>10.2</v>
       </c>
       <c r="R20" s="2">
         <v>26591</v>
@@ -1110,16 +1203,22 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>34.4</v>
+        <v>34.5</v>
       </c>
       <c r="E21">
         <v>12.2</v>
       </c>
       <c r="F21">
-        <v>23.3</v>
-      </c>
-      <c r="L21">
-        <v>14</v>
+        <v>23.2</v>
+      </c>
+      <c r="H21">
+        <v>13.7</v>
+      </c>
+      <c r="J21">
+        <v>27.7</v>
+      </c>
+      <c r="K21">
+        <v>7.3</v>
       </c>
       <c r="R21" s="2">
         <v>26592</v>
@@ -1145,13 +1244,13 @@
         <v>33.8</v>
       </c>
       <c r="E22">
-        <v>20.6</v>
+        <v>10.6</v>
       </c>
       <c r="F22">
         <v>22.2</v>
       </c>
-      <c r="J22">
-        <v>28.5</v>
+      <c r="I22">
+        <v>33.6</v>
       </c>
       <c r="R22" s="2">
         <v>26593</v>
@@ -1182,6 +1281,9 @@
       <c r="F23">
         <v>22.8</v>
       </c>
+      <c r="I23">
+        <v>26</v>
+      </c>
       <c r="R23" s="2">
         <v>26594</v>
       </c>
@@ -1203,14 +1305,17 @@
         <v>23</v>
       </c>
       <c r="D24">
-        <v>30.8</v>
+        <v>39.8</v>
       </c>
       <c r="E24">
-        <v>15.6</v>
+        <v>6.6</v>
       </c>
       <c r="F24">
         <v>23.2</v>
       </c>
+      <c r="I24">
+        <v>19</v>
+      </c>
       <c r="R24" s="2">
         <v>26595</v>
       </c>
@@ -1235,10 +1340,13 @@
         <v>30.4</v>
       </c>
       <c r="E25">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="F25">
-        <v>23.7</v>
+        <v>23.6</v>
+      </c>
+      <c r="I25">
+        <v>30.8</v>
       </c>
       <c r="R25" s="2">
         <v>26596</v>
@@ -1260,13 +1368,16 @@
       <c r="C26">
         <v>25</v>
       </c>
+      <c r="D26">
+        <v>25.8</v>
+      </c>
       <c r="E26">
-        <v>11.9</v>
-      </c>
-      <c r="F26">
-        <v>18.7</v>
-      </c>
-      <c r="N26" t="s">
+        <v>11.2</v>
+      </c>
+      <c r="I26">
+        <v>24.6</v>
+      </c>
+      <c r="P26" t="s">
         <v>20</v>
       </c>
       <c r="R26" s="2">
@@ -1289,17 +1400,23 @@
       <c r="C27">
         <v>26</v>
       </c>
+      <c r="D27">
+        <v>29.2</v>
+      </c>
+      <c r="E27">
+        <v>14.2</v>
+      </c>
+      <c r="F27">
+        <v>21.7</v>
+      </c>
       <c r="H27">
-        <v>15.1</v>
+        <v>15.8</v>
       </c>
       <c r="I27">
         <v>28.7</v>
       </c>
-      <c r="J27">
-        <v>24.8</v>
-      </c>
-      <c r="L27">
-        <v>15.5</v>
+      <c r="K27">
+        <v>10.2</v>
       </c>
       <c r="R27" s="2">
         <v>26598</v>
@@ -1336,11 +1453,8 @@
       <c r="I28">
         <v>30</v>
       </c>
-      <c r="J28">
-        <v>26</v>
-      </c>
-      <c r="L28">
-        <v>15</v>
+      <c r="K28">
+        <v>10.4</v>
       </c>
       <c r="R28" s="2">
         <v>26599</v>
@@ -1363,13 +1477,13 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="E29">
         <v>16.2</v>
       </c>
       <c r="F29">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="H29">
         <v>18</v>
@@ -1377,11 +1491,11 @@
       <c r="I29">
         <v>29.8</v>
       </c>
-      <c r="J29">
-        <v>27.5</v>
+      <c r="K29">
+        <v>11.1</v>
       </c>
       <c r="L29">
-        <v>15.5</v>
+        <v>5.9</v>
       </c>
       <c r="R29" s="2">
         <v>26600</v>
@@ -1407,10 +1521,10 @@
         <v>31.2</v>
       </c>
       <c r="E30">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="F30">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="H30">
         <v>16.8</v>
@@ -1418,11 +1532,8 @@
       <c r="I30">
         <v>26.4</v>
       </c>
-      <c r="J30">
-        <v>18</v>
-      </c>
-      <c r="L30">
-        <v>6.8</v>
+      <c r="K30">
+        <v>10.9</v>
       </c>
       <c r="R30" s="2">
         <v>26601</v>
@@ -1448,10 +1559,10 @@
         <v>30.6</v>
       </c>
       <c r="E31">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="F31">
-        <v>23.3</v>
+        <v>23.4</v>
       </c>
       <c r="H31">
         <v>17.7</v>
@@ -1462,8 +1573,8 @@
       <c r="J31">
         <v>25.7</v>
       </c>
-      <c r="L31">
-        <v>4.6</v>
+      <c r="K31">
+        <v>11.9</v>
       </c>
       <c r="R31" s="2">
         <v>26602</v>
@@ -1500,11 +1611,8 @@
       <c r="I32">
         <v>29.2</v>
       </c>
-      <c r="J32">
-        <v>21.2</v>
-      </c>
-      <c r="L32">
-        <v>14.4</v>
+      <c r="K32">
+        <v>9.800000000000001</v>
       </c>
       <c r="R32" s="2">
         <v>26603</v>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
@@ -522,12 +522,18 @@
       <c r="F2">
         <v>21.6</v>
       </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
       <c r="H2">
         <v>11.1</v>
       </c>
       <c r="I2">
         <v>33.3</v>
       </c>
+      <c r="K2">
+        <v>4.6</v>
+      </c>
       <c r="L2">
         <v>13.7</v>
       </c>
@@ -560,12 +566,21 @@
       <c r="F3">
         <v>21.7</v>
       </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
       <c r="H3">
         <v>12.2</v>
       </c>
       <c r="I3">
         <v>31.7</v>
       </c>
+      <c r="J3">
+        <v>28.4</v>
+      </c>
+      <c r="K3">
+        <v>5.5</v>
+      </c>
       <c r="L3">
         <v>14</v>
       </c>
@@ -598,12 +613,21 @@
       <c r="F4">
         <v>22.3</v>
       </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
       <c r="H4">
         <v>12.2</v>
       </c>
       <c r="I4">
         <v>32.7</v>
       </c>
+      <c r="J4">
+        <v>28.2</v>
+      </c>
+      <c r="K4">
+        <v>6</v>
+      </c>
       <c r="L4">
         <v>15.2</v>
       </c>
@@ -636,12 +660,21 @@
       <c r="F5">
         <v>23.1</v>
       </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
       <c r="H5">
         <v>12.5</v>
       </c>
       <c r="I5">
         <v>34.7</v>
       </c>
+      <c r="J5">
+        <v>28.9</v>
+      </c>
+      <c r="K5">
+        <v>5.6</v>
+      </c>
       <c r="L5">
         <v>13.8</v>
       </c>
@@ -674,12 +707,18 @@
       <c r="F6">
         <v>22.7</v>
       </c>
+      <c r="G6">
+        <v>0.2</v>
+      </c>
       <c r="H6">
         <v>19.1</v>
       </c>
       <c r="I6">
         <v>32.6</v>
       </c>
+      <c r="K6">
+        <v>10.8</v>
+      </c>
       <c r="L6">
         <v>15.1</v>
       </c>
@@ -703,8 +742,17 @@
       <c r="C7">
         <v>6</v>
       </c>
+      <c r="D7">
+        <v>30.5</v>
+      </c>
+      <c r="E7">
+        <v>17.2</v>
+      </c>
+      <c r="F7">
+        <v>23.9</v>
+      </c>
       <c r="G7">
-        <v>11.7</v>
+        <v>1.7</v>
       </c>
       <c r="H7">
         <v>18.2</v>
@@ -715,6 +763,15 @@
       <c r="J7">
         <v>21.7</v>
       </c>
+      <c r="K7">
+        <v>6.4</v>
+      </c>
+      <c r="L7">
+        <v>5.7</v>
+      </c>
+      <c r="M7">
+        <v>14.5</v>
+      </c>
       <c r="R7" s="2">
         <v>26578</v>
       </c>
@@ -735,6 +792,15 @@
       <c r="C8">
         <v>7</v>
       </c>
+      <c r="D8">
+        <v>31.1</v>
+      </c>
+      <c r="E8">
+        <v>12.3</v>
+      </c>
+      <c r="F8">
+        <v>21.7</v>
+      </c>
       <c r="G8">
         <v>0</v>
       </c>
@@ -745,7 +811,16 @@
         <v>31.3</v>
       </c>
       <c r="J8">
-        <v>27</v>
+        <v>21.8</v>
+      </c>
+      <c r="K8">
+        <v>12.7</v>
+      </c>
+      <c r="L8">
+        <v>0.9</v>
+      </c>
+      <c r="M8">
+        <v>10</v>
       </c>
       <c r="R8" s="2">
         <v>26579</v>
@@ -788,6 +863,12 @@
       <c r="J9">
         <v>27</v>
       </c>
+      <c r="K9">
+        <v>10.6</v>
+      </c>
+      <c r="L9">
+        <v>1.7</v>
+      </c>
       <c r="M9">
         <v>7.3</v>
       </c>
@@ -818,7 +899,7 @@
         <v>17.4</v>
       </c>
       <c r="F10">
-        <v>24.5</v>
+        <v>24.6</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -832,6 +913,15 @@
       <c r="J10">
         <v>27</v>
       </c>
+      <c r="K10">
+        <v>12</v>
+      </c>
+      <c r="L10">
+        <v>2.5</v>
+      </c>
+      <c r="M10">
+        <v>14.5</v>
+      </c>
       <c r="R10" s="2">
         <v>26581</v>
       </c>
@@ -853,13 +943,13 @@
         <v>10</v>
       </c>
       <c r="D11">
-        <v>31.2</v>
+        <v>31.3</v>
       </c>
       <c r="E11">
         <v>15</v>
       </c>
       <c r="F11">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -873,6 +963,15 @@
       <c r="J11">
         <v>27.1</v>
       </c>
+      <c r="K11">
+        <v>10.4</v>
+      </c>
+      <c r="L11">
+        <v>1.7</v>
+      </c>
+      <c r="M11">
+        <v>14</v>
+      </c>
       <c r="R11" s="2">
         <v>26582</v>
       </c>
@@ -894,13 +993,28 @@
         <v>11</v>
       </c>
       <c r="D12">
-        <v>33</v>
+        <v>32.9</v>
       </c>
       <c r="E12">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F12">
-        <v>22.7</v>
+        <v>22.6</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>13.5</v>
+      </c>
+      <c r="I12">
+        <v>32.1</v>
+      </c>
+      <c r="J12">
+        <v>28.1</v>
+      </c>
+      <c r="K12">
+        <v>7.6</v>
       </c>
       <c r="R12" s="2">
         <v>26583</v>
@@ -931,12 +1045,27 @@
       <c r="F13">
         <v>22.9</v>
       </c>
+      <c r="G13">
+        <v>2.6</v>
+      </c>
+      <c r="H13">
+        <v>13.5</v>
+      </c>
       <c r="I13">
         <v>32</v>
       </c>
+      <c r="J13">
+        <v>26.9</v>
+      </c>
+      <c r="K13">
+        <v>7.9</v>
+      </c>
       <c r="L13">
         <v>0</v>
       </c>
+      <c r="M13">
+        <v>12.9</v>
+      </c>
       <c r="R13" s="2">
         <v>26584</v>
       </c>
@@ -966,12 +1095,27 @@
       <c r="F14">
         <v>20.3</v>
       </c>
+      <c r="G14">
+        <v>0.7</v>
+      </c>
+      <c r="H14">
+        <v>18</v>
+      </c>
       <c r="I14">
         <v>28.3</v>
       </c>
+      <c r="J14">
+        <v>22.2</v>
+      </c>
+      <c r="K14">
+        <v>12.6</v>
+      </c>
       <c r="L14">
         <v>5</v>
       </c>
+      <c r="M14">
+        <v>12.4</v>
+      </c>
       <c r="R14" s="2">
         <v>26585</v>
       </c>
@@ -1001,6 +1145,27 @@
       <c r="F15">
         <v>23.6</v>
       </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>17.7</v>
+      </c>
+      <c r="I15">
+        <v>30.7</v>
+      </c>
+      <c r="J15">
+        <v>26.3</v>
+      </c>
+      <c r="K15">
+        <v>11.5</v>
+      </c>
+      <c r="L15">
+        <v>3</v>
+      </c>
+      <c r="M15">
+        <v>14.5</v>
+      </c>
       <c r="R15" s="2">
         <v>26586</v>
       </c>
@@ -1030,6 +1195,27 @@
       <c r="F16">
         <v>22.5</v>
       </c>
+      <c r="G16">
+        <v>0</v>
+      </c>
+      <c r="H16">
+        <v>16.4</v>
+      </c>
+      <c r="I16">
+        <v>31.3</v>
+      </c>
+      <c r="J16">
+        <v>27</v>
+      </c>
+      <c r="K16">
+        <v>10.7</v>
+      </c>
+      <c r="L16">
+        <v>1.5</v>
+      </c>
+      <c r="M16">
+        <v>14.6</v>
+      </c>
       <c r="R16" s="2">
         <v>26587</v>
       </c>
@@ -1051,14 +1237,17 @@
         <v>16</v>
       </c>
       <c r="D17">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="E17">
-        <v>17.8</v>
+        <v>17.7</v>
       </c>
       <c r="F17">
         <v>24.8</v>
       </c>
+      <c r="G17">
+        <v>10.9</v>
+      </c>
       <c r="H17">
         <v>19.8</v>
       </c>
@@ -1095,11 +1284,17 @@
         <v>14.8</v>
       </c>
       <c r="F18">
-        <v>22.6</v>
+        <v>22.1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
       </c>
       <c r="H18">
         <v>15.9</v>
       </c>
+      <c r="I18">
+        <v>29.3</v>
+      </c>
       <c r="J18">
         <v>26.4</v>
       </c>
@@ -1135,15 +1330,24 @@
       <c r="F19">
         <v>23.5</v>
       </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
       <c r="H19">
         <v>16.3</v>
       </c>
+      <c r="I19">
+        <v>30.8</v>
+      </c>
       <c r="J19">
         <v>27.2</v>
       </c>
       <c r="K19">
         <v>10.8</v>
       </c>
+      <c r="M19">
+        <v>6.4</v>
+      </c>
       <c r="R19" s="2">
         <v>26590</v>
       </c>
@@ -1173,6 +1377,9 @@
       <c r="F20">
         <v>23.9</v>
       </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
       <c r="H20">
         <v>16.5</v>
       </c>
@@ -1180,7 +1387,7 @@
         <v>27.7</v>
       </c>
       <c r="K20">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="R20" s="2">
         <v>26591</v>
@@ -1203,17 +1410,23 @@
         <v>20</v>
       </c>
       <c r="D21">
-        <v>34.5</v>
+        <v>34.4</v>
       </c>
       <c r="E21">
         <v>12.2</v>
       </c>
       <c r="F21">
-        <v>23.2</v>
+        <v>23.3</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
       </c>
       <c r="H21">
         <v>13.7</v>
       </c>
+      <c r="I21">
+        <v>33.5</v>
+      </c>
       <c r="J21">
         <v>27.7</v>
       </c>
@@ -1249,9 +1462,18 @@
       <c r="F22">
         <v>22.2</v>
       </c>
+      <c r="H22">
+        <v>12</v>
+      </c>
       <c r="I22">
         <v>33.6</v>
       </c>
+      <c r="K22">
+        <v>5.7</v>
+      </c>
+      <c r="L22">
+        <v>14.1</v>
+      </c>
       <c r="R22" s="2">
         <v>26593</v>
       </c>
@@ -1273,17 +1495,26 @@
         <v>22</v>
       </c>
       <c r="D23">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="E23">
         <v>14.6</v>
       </c>
       <c r="F23">
-        <v>22.8</v>
+        <v>22.9</v>
+      </c>
+      <c r="H23">
+        <v>18.7</v>
       </c>
       <c r="I23">
         <v>26</v>
       </c>
+      <c r="K23">
+        <v>11.2</v>
+      </c>
+      <c r="L23">
+        <v>7.3</v>
+      </c>
       <c r="R23" s="2">
         <v>26594</v>
       </c>
@@ -1313,9 +1544,18 @@
       <c r="F24">
         <v>23.2</v>
       </c>
+      <c r="H24">
+        <v>17.2</v>
+      </c>
       <c r="I24">
         <v>19</v>
       </c>
+      <c r="K24">
+        <v>11.4</v>
+      </c>
+      <c r="L24">
+        <v>13.4</v>
+      </c>
       <c r="R24" s="2">
         <v>26595</v>
       </c>
@@ -1345,8 +1585,17 @@
       <c r="F25">
         <v>23.6</v>
       </c>
+      <c r="H25">
+        <v>18.2</v>
+      </c>
       <c r="I25">
-        <v>30.8</v>
+        <v>30.3</v>
+      </c>
+      <c r="K25">
+        <v>12.6</v>
+      </c>
+      <c r="L25">
+        <v>6.7</v>
       </c>
       <c r="R25" s="2">
         <v>26596</v>
@@ -1374,9 +1623,18 @@
       <c r="E26">
         <v>11.2</v>
       </c>
+      <c r="H26">
+        <v>17.8</v>
+      </c>
       <c r="I26">
         <v>24.6</v>
       </c>
+      <c r="K26">
+        <v>12.3</v>
+      </c>
+      <c r="L26">
+        <v>8</v>
+      </c>
       <c r="P26" t="s">
         <v>20</v>
       </c>
@@ -1410,14 +1668,20 @@
         <v>21.7</v>
       </c>
       <c r="H27">
-        <v>15.8</v>
+        <v>15</v>
       </c>
       <c r="I27">
         <v>28.7</v>
       </c>
+      <c r="J27">
+        <v>24.8</v>
+      </c>
       <c r="K27">
         <v>10.2</v>
       </c>
+      <c r="L27">
+        <v>7</v>
+      </c>
       <c r="R27" s="2">
         <v>26598</v>
       </c>
@@ -1448,13 +1712,19 @@
         <v>22.7</v>
       </c>
       <c r="H28">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="I28">
         <v>30</v>
       </c>
+      <c r="J28">
+        <v>26</v>
+      </c>
       <c r="K28">
-        <v>10.4</v>
+        <v>5.6</v>
+      </c>
+      <c r="M28">
+        <v>7.1</v>
       </c>
       <c r="R28" s="2">
         <v>26599</v>
@@ -1486,13 +1756,16 @@
         <v>23.9</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="I29">
         <v>29.8</v>
       </c>
+      <c r="J29">
+        <v>27.5</v>
+      </c>
       <c r="K29">
-        <v>11.1</v>
+        <v>7.4</v>
       </c>
       <c r="L29">
         <v>5.9</v>
@@ -1532,9 +1805,15 @@
       <c r="I30">
         <v>26.4</v>
       </c>
+      <c r="J30">
+        <v>19</v>
+      </c>
       <c r="K30">
         <v>10.9</v>
       </c>
+      <c r="L30">
+        <v>6.8</v>
+      </c>
       <c r="R30" s="2">
         <v>26601</v>
       </c>
@@ -1611,8 +1890,14 @@
       <c r="I32">
         <v>29.2</v>
       </c>
+      <c r="J32">
+        <v>21.2</v>
+      </c>
       <c r="K32">
         <v>9.800000000000001</v>
+      </c>
+      <c r="M32">
+        <v>10.7</v>
       </c>
       <c r="R32" s="2">
         <v>26603</v>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -743,10 +743,10 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E7">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="F7">
         <v>23.9</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="I11">
         <v>31</v>
@@ -996,10 +996,10 @@
         <v>32.9</v>
       </c>
       <c r="E12">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="F12">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1016,6 +1016,9 @@
       <c r="K12">
         <v>7.6</v>
       </c>
+      <c r="L12">
+        <v>2.7</v>
+      </c>
       <c r="R12" s="2">
         <v>26583</v>
       </c>
@@ -1037,10 +1040,10 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="E13">
-        <v>12.4</v>
+        <v>12.3</v>
       </c>
       <c r="F13">
         <v>22.9</v>
@@ -1063,9 +1066,6 @@
       <c r="L13">
         <v>0</v>
       </c>
-      <c r="M13">
-        <v>12.9</v>
-      </c>
       <c r="R13" s="2">
         <v>26584</v>
       </c>
@@ -1087,13 +1087,13 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>23.4</v>
+        <v>31.4</v>
       </c>
       <c r="E14">
         <v>17.2</v>
       </c>
       <c r="F14">
-        <v>20.3</v>
+        <v>24.3</v>
       </c>
       <c r="G14">
         <v>0.7</v>
@@ -1140,10 +1140,10 @@
         <v>30.9</v>
       </c>
       <c r="E15">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F15">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1284,7 +1284,7 @@
         <v>14.8</v>
       </c>
       <c r="F18">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1513,7 +1513,7 @@
         <v>11.2</v>
       </c>
       <c r="L23">
-        <v>7.3</v>
+        <v>14.7</v>
       </c>
       <c r="R23" s="2">
         <v>26594</v>
@@ -1535,9 +1535,6 @@
       <c r="C24">
         <v>23</v>
       </c>
-      <c r="D24">
-        <v>39.8</v>
-      </c>
       <c r="E24">
         <v>6.6</v>
       </c>
@@ -1556,6 +1553,9 @@
       <c r="L24">
         <v>13.4</v>
       </c>
+      <c r="N24" t="s">
+        <v>20</v>
+      </c>
       <c r="R24" s="2">
         <v>26595</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>25</v>
       </c>
       <c r="D26">
-        <v>25.8</v>
+        <v>25.4</v>
       </c>
       <c r="E26">
         <v>11.2</v>
@@ -1712,7 +1712,7 @@
         <v>22.7</v>
       </c>
       <c r="H28">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="I28">
         <v>30</v>
@@ -1721,7 +1721,7 @@
         <v>26</v>
       </c>
       <c r="K28">
-        <v>5.6</v>
+        <v>10.4</v>
       </c>
       <c r="M28">
         <v>7.1</v>
@@ -1747,16 +1747,16 @@
         <v>28</v>
       </c>
       <c r="D29">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="E29">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="F29">
-        <v>23.9</v>
+        <v>23.8</v>
       </c>
       <c r="H29">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="I29">
         <v>29.8</v>
@@ -1765,7 +1765,7 @@
         <v>27.5</v>
       </c>
       <c r="K29">
-        <v>7.4</v>
+        <v>11.9</v>
       </c>
       <c r="L29">
         <v>5.9</v>
@@ -1835,13 +1835,13 @@
         <v>30</v>
       </c>
       <c r="D31">
-        <v>30.6</v>
+        <v>30.5</v>
       </c>
       <c r="E31">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="F31">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="H31">
         <v>17.7</v>
@@ -1876,10 +1876,10 @@
         <v>31</v>
       </c>
       <c r="D32">
-        <v>30.8</v>
+        <v>30.7</v>
       </c>
       <c r="E32">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="F32">
         <v>22.9</v>
@@ -1895,6 +1895,9 @@
       </c>
       <c r="K32">
         <v>9.800000000000001</v>
+      </c>
+      <c r="L32">
+        <v>3.4</v>
       </c>
       <c r="M32">
         <v>10.7</v>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Year</t>
   </si>
@@ -743,10 +743,10 @@
         <v>6</v>
       </c>
       <c r="D7">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E7">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="F7">
         <v>23.9</v>
@@ -955,7 +955,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="I11">
         <v>31</v>
@@ -996,10 +996,10 @@
         <v>32.9</v>
       </c>
       <c r="E12">
-        <v>12.4</v>
+        <v>12.5</v>
       </c>
       <c r="F12">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -1040,10 +1040,10 @@
         <v>12</v>
       </c>
       <c r="D13">
-        <v>33.4</v>
+        <v>33.5</v>
       </c>
       <c r="E13">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="F13">
         <v>22.9</v>
@@ -1066,6 +1066,9 @@
       <c r="L13">
         <v>0</v>
       </c>
+      <c r="M13">
+        <v>12.9</v>
+      </c>
       <c r="R13" s="2">
         <v>26584</v>
       </c>
@@ -1087,13 +1090,13 @@
         <v>13</v>
       </c>
       <c r="D14">
-        <v>31.4</v>
+        <v>23.4</v>
       </c>
       <c r="E14">
         <v>17.2</v>
       </c>
       <c r="F14">
-        <v>24.3</v>
+        <v>20.3</v>
       </c>
       <c r="G14">
         <v>0.7</v>
@@ -1140,10 +1143,10 @@
         <v>30.9</v>
       </c>
       <c r="E15">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="F15">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -1284,7 +1287,7 @@
         <v>14.8</v>
       </c>
       <c r="F18">
-        <v>22.2</v>
+        <v>22.5</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -1383,6 +1386,9 @@
       <c r="H20">
         <v>16.5</v>
       </c>
+      <c r="I20">
+        <v>32.1</v>
+      </c>
       <c r="J20">
         <v>27.7</v>
       </c>
@@ -1535,6 +1541,9 @@
       <c r="C24">
         <v>23</v>
       </c>
+      <c r="D24">
+        <v>39.8</v>
+      </c>
       <c r="E24">
         <v>6.6</v>
       </c>
@@ -1553,9 +1562,6 @@
       <c r="L24">
         <v>13.4</v>
       </c>
-      <c r="N24" t="s">
-        <v>20</v>
-      </c>
       <c r="R24" s="2">
         <v>26595</v>
       </c>
@@ -1712,7 +1718,7 @@
         <v>22.7</v>
       </c>
       <c r="H28">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="I28">
         <v>30</v>
@@ -1721,7 +1727,10 @@
         <v>26</v>
       </c>
       <c r="K28">
-        <v>10.4</v>
+        <v>5.6</v>
+      </c>
+      <c r="L28">
+        <v>4.3</v>
       </c>
       <c r="M28">
         <v>7.1</v>
@@ -1756,7 +1765,7 @@
         <v>23.8</v>
       </c>
       <c r="H29">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="I29">
         <v>29.8</v>
@@ -1765,11 +1774,14 @@
         <v>27.5</v>
       </c>
       <c r="K29">
-        <v>11.9</v>
+        <v>7.4</v>
       </c>
       <c r="L29">
         <v>5.9</v>
       </c>
+      <c r="M29">
+        <v>7.6</v>
+      </c>
       <c r="R29" s="2">
         <v>26600</v>
       </c>
@@ -1895,12 +1907,6 @@
       </c>
       <c r="K32">
         <v>9.800000000000001</v>
-      </c>
-      <c r="L32">
-        <v>3.4</v>
-      </c>
-      <c r="M32">
-        <v>10.7</v>
       </c>
       <c r="R32" s="2">
         <v>26603</v>

--- a/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/501/Daily_temperature_and_precipitation_station_501.xlsx
@@ -766,9 +766,6 @@
       <c r="K7">
         <v>6.4</v>
       </c>
-      <c r="L7">
-        <v>5.7</v>
-      </c>
       <c r="M7">
         <v>14.5</v>
       </c>
@@ -816,11 +813,8 @@
       <c r="K8">
         <v>12.7</v>
       </c>
-      <c r="L8">
-        <v>0.9</v>
-      </c>
       <c r="M8">
-        <v>10</v>
+        <v>15.1</v>
       </c>
       <c r="R8" s="2">
         <v>26579</v>
@@ -866,11 +860,8 @@
       <c r="K9">
         <v>10.6</v>
       </c>
-      <c r="L9">
-        <v>1.7</v>
-      </c>
       <c r="M9">
-        <v>7.3</v>
+        <v>15.1</v>
       </c>
       <c r="R9" s="2">
         <v>26580</v>
@@ -916,9 +907,6 @@
       <c r="K10">
         <v>12</v>
       </c>
-      <c r="L10">
-        <v>2.5</v>
-      </c>
       <c r="M10">
         <v>14.5</v>
       </c>
@@ -966,9 +954,6 @@
       <c r="K11">
         <v>10.4</v>
       </c>
-      <c r="L11">
-        <v>1.7</v>
-      </c>
       <c r="M11">
         <v>14</v>
       </c>
@@ -1016,8 +1001,8 @@
       <c r="K12">
         <v>7.6</v>
       </c>
-      <c r="L12">
-        <v>2.7</v>
+      <c r="M12">
+        <v>14.4</v>
       </c>
       <c r="R12" s="2">
         <v>26583</v>
@@ -1063,9 +1048,6 @@
       <c r="K13">
         <v>7.9</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
       <c r="M13">
         <v>12.9</v>
       </c>
@@ -1113,9 +1095,6 @@
       <c r="K14">
         <v>12.6</v>
       </c>
-      <c r="L14">
-        <v>5</v>
-      </c>
       <c r="M14">
         <v>12.4</v>
       </c>
@@ -1163,9 +1142,6 @@
       <c r="K15">
         <v>11.5</v>
       </c>
-      <c r="L15">
-        <v>3</v>
-      </c>
       <c r="M15">
         <v>14.5</v>
       </c>
@@ -1213,9 +1189,6 @@
       <c r="K16">
         <v>10.7</v>
       </c>
-      <c r="L16">
-        <v>1.5</v>
-      </c>
       <c r="M16">
         <v>14.6</v>
       </c>
@@ -1348,9 +1321,6 @@
       <c r="K19">
         <v>10.8</v>
       </c>
-      <c r="M19">
-        <v>6.4</v>
-      </c>
       <c r="R19" s="2">
         <v>26590</v>
       </c>
@@ -1393,7 +1363,7 @@
         <v>27.7</v>
       </c>
       <c r="K20">
-        <v>5.1</v>
+        <v>10.2</v>
       </c>
       <c r="R20" s="2">
         <v>26591</v>
@@ -1601,7 +1571,7 @@
         <v>12.6</v>
       </c>
       <c r="L25">
-        <v>6.7</v>
+        <v>15.9</v>
       </c>
       <c r="R25" s="2">
         <v>26596</v>
@@ -1639,7 +1609,7 @@
         <v>12.3</v>
       </c>
       <c r="L26">
-        <v>8</v>
+        <v>14.5</v>
       </c>
       <c r="P26" t="s">
         <v>20</v>
@@ -1685,9 +1655,6 @@
       <c r="K27">
         <v>10.2</v>
       </c>
-      <c r="L27">
-        <v>7</v>
-      </c>
       <c r="R27" s="2">
         <v>26598</v>
       </c>
@@ -1727,13 +1694,7 @@
         <v>26</v>
       </c>
       <c r="K28">
-        <v>5.6</v>
-      </c>
-      <c r="L28">
-        <v>4.3</v>
-      </c>
-      <c r="M28">
-        <v>7.1</v>
+        <v>10.4</v>
       </c>
       <c r="R28" s="2">
         <v>26599</v>
@@ -1774,13 +1735,7 @@
         <v>27.5</v>
       </c>
       <c r="K29">
-        <v>7.4</v>
-      </c>
-      <c r="L29">
-        <v>5.9</v>
-      </c>
-      <c r="M29">
-        <v>7.6</v>
+        <v>11.9</v>
       </c>
       <c r="R29" s="2">
         <v>26600</v>
@@ -1822,9 +1777,6 @@
       </c>
       <c r="K30">
         <v>10.9</v>
-      </c>
-      <c r="L30">
-        <v>6.8</v>
       </c>
       <c r="R30" s="2">
         <v>26601</v>
